--- a/src/test/resources/FilterData.xlsx
+++ b/src/test/resources/FilterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coder\Selenium\Totoday\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1C8833-363F-4FA4-AD7D-849AF2CFE2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD8947F-8B43-43F4-B406-2B3F17ACD186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="1650" windowWidth="21600" windowHeight="11175" activeTab="1" xr2:uid="{BD033642-A450-43D2-AA57-A2209245F063}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD033642-A450-43D2-AA57-A2209245F063}"/>
   </bookViews>
   <sheets>
     <sheet name="ColorData" sheetId="1" r:id="rId1"/>
@@ -556,6 +556,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC531DFA-039F-4B79-A24E-A5CD4FC86A20}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="68.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
